--- a/KatalonData/RADTestData/ChangePaymentMethodPersonal.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethodPersonal.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="396">
   <si>
     <t>Result</t>
   </si>
@@ -717,12 +717,529 @@
   </si>
   <si>
     <t>Mon Aug 03 15:21:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:13:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:15:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:17:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:17:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:20:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:22:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:23:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:24:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:25:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:26:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:27:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:28:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:29:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:31:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:32:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:34:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:35:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:37:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:38:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:39:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:40:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:41:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:43:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:44:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:45:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:46:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:46:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:47:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:49:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:51:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:52:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:53:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:54:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:55:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:56:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:57:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 05:59:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:00:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:01:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:03:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:08:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:11:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:12:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:13:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:15:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:17:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:19:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:20:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:22:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:23:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:24:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:25:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:26:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:27:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:28:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:30:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:32:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:33:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:34:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:35:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:38:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:39:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:40:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:41:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:42:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:43:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:44:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:46:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:47:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:48:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:50:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:52:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:53:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:54:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:55:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:57:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 06:58:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:00:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:01:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:02:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:05:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:06:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:07:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:08:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:09:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:10:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:12:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:13:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:14:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:15:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:17:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:18:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:19:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:20:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:22:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:23:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:24:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:27:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:28:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:29:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:30:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:31:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:32:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:33:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:34:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:35:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:36:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:37:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:38:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:39:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:42:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:43:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:45:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:46:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:47:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:48:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:50:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:51:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:52:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:53:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:54:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:55:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:56:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:57:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:58:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 07:59:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:01:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:02:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:03:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:04:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:05:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:06:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:08:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:09:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:10:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:11:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:12:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:13:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:14:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:15:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:16:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:17:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:18:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:19:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:20:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:21:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:22:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:23:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:25:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:26:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Aug 17 08:27:33 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1095,17 +1612,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1145,7 +1662,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>231</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1174,7 +1691,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1203,7 +1720,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>120</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1235,7 +1752,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1267,7 +1784,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>235</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1299,7 +1816,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1331,7 +1848,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1364,16 +1881,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1413,7 +1930,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1436,7 +1953,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1459,7 +1976,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1482,7 +1999,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1508,7 +2025,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1534,7 +2051,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>130</v>
+        <v>243</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1557,7 +2074,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1580,7 +2097,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1603,7 +2120,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1626,7 +2143,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>247</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1649,7 +2166,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1672,7 +2189,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>249</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1695,7 +2212,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1718,7 +2235,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>251</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1738,7 +2255,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1764,7 +2281,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1787,7 +2304,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>141</v>
+        <v>254</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1827,7 +2344,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>142</v>
+        <v>255</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1872,15 +2389,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1917,7 +2434,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>256</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1943,7 +2460,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>144</v>
+        <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1966,7 +2483,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1992,7 +2509,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>146</v>
+        <v>259</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2018,7 +2535,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2044,7 +2561,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>148</v>
+        <v>261</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2079,17 +2596,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
-    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2138,7 +2655,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>322</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2161,7 +2678,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>150</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2187,7 +2704,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>324</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2213,7 +2730,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2239,7 +2756,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>326</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2265,7 +2782,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2288,7 +2805,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>328</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2314,7 +2831,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>329</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2340,7 +2857,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>330</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2366,7 +2883,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>331</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2392,7 +2909,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>159</v>
+        <v>332</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2415,7 +2932,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>333</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2441,7 +2958,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>334</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2467,7 +2984,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>335</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2493,7 +3010,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>336</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2519,7 +3036,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>164</v>
+        <v>337</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2548,7 +3065,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>165</v>
+        <v>338</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2577,7 +3094,7 @@
         <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>339</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2606,7 +3123,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>167</v>
+        <v>340</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2629,7 +3146,7 @@
         <v>114</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>168</v>
+        <v>341</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2658,7 +3175,7 @@
         <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>169</v>
+        <v>342</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2687,7 +3204,7 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>170</v>
+        <v>343</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2713,7 +3230,7 @@
         <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>344</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2742,7 +3259,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>172</v>
+        <v>345</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2774,7 +3291,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>173</v>
+        <v>346</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2803,7 +3320,7 @@
         <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>174</v>
+        <v>347</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2832,7 +3349,7 @@
         <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>175</v>
+        <v>348</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2864,7 +3381,7 @@
         <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>176</v>
+        <v>349</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2893,7 +3410,7 @@
         <v>114</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>177</v>
+        <v>350</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2922,7 +3439,7 @@
         <v>114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2951,7 +3468,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>179</v>
+        <v>352</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2974,7 +3491,7 @@
         <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>180</v>
+        <v>353</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3003,7 +3520,7 @@
         <v>114</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>354</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3032,7 +3549,7 @@
         <v>114</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>355</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3058,7 +3575,7 @@
         <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>356</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3087,7 +3604,7 @@
         <v>114</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>357</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3119,7 +3636,7 @@
         <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>185</v>
+        <v>358</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3148,7 +3665,7 @@
         <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>186</v>
+        <v>359</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3177,7 +3694,7 @@
         <v>114</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>187</v>
+        <v>360</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3209,7 +3726,7 @@
         <v>114</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>188</v>
+        <v>361</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3238,7 +3755,7 @@
         <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>189</v>
+        <v>362</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3267,7 +3784,7 @@
         <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>190</v>
+        <v>363</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3296,7 +3813,7 @@
         <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>364</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3319,7 +3836,7 @@
         <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>192</v>
+        <v>365</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3348,7 +3865,7 @@
         <v>114</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>193</v>
+        <v>366</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3377,7 +3894,7 @@
         <v>114</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>194</v>
+        <v>367</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3403,7 +3920,7 @@
         <v>114</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3432,7 +3949,7 @@
         <v>114</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>196</v>
+        <v>369</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3464,7 +3981,7 @@
         <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>197</v>
+        <v>370</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3493,7 +4010,7 @@
         <v>114</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>198</v>
+        <v>371</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3522,7 +4039,7 @@
         <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>199</v>
+        <v>372</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3554,7 +4071,7 @@
         <v>114</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3574,10 +4091,10 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A54" s="1" t="s">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>218</v>
+        <v>374</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>29</v>
@@ -3623,7 +4140,7 @@
         <v>114</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>201</v>
+        <v>375</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3646,7 +4163,7 @@
         <v>114</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>376</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>29</v>
@@ -3692,7 +4209,7 @@
         <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>202</v>
+        <v>377</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3715,7 +4232,7 @@
         <v>114</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>220</v>
+        <v>378</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>29</v>
@@ -3761,7 +4278,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>379</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -3787,7 +4304,7 @@
         <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>380</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -3813,7 +4330,7 @@
         <v>114</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>205</v>
+        <v>381</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -3849,14 +4366,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3890,7 +4407,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>207</v>
+        <v>383</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3913,7 +4430,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>208</v>
+        <v>384</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3936,7 +4453,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>209</v>
+        <v>385</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3959,7 +4476,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>210</v>
+        <v>386</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3982,7 +4499,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>211</v>
+        <v>387</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4005,7 +4522,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>221</v>
+        <v>388</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -4025,7 +4542,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>222</v>
+        <v>389</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -4044,8 +4561,8 @@
       <c r="A9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B9" t="s">
-        <v>223</v>
+      <c r="B9" t="s" s="1">
+        <v>390</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -4070,14 +4587,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4108,7 +4625,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4131,7 +4648,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>392</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4154,7 +4671,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>214</v>
+        <v>393</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4177,7 +4694,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>215</v>
+        <v>394</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4200,7 +4717,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>216</v>
+        <v>395</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4228,12 +4745,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4261,7 +4778,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>206</v>
+        <v>382</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
